--- a/XBRL-template-MPERS/backup-originals/Company/03-SOPL-Function.xlsx
+++ b/XBRL-template-MPERS/backup-originals/Company/03-SOPL-Function.xlsx
@@ -659,10 +659,18 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Profit (loss)</t>
-        </is>
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>*Profit (loss)</t>
+        </is>
+      </c>
+      <c r="B29">
+        <f>1*B26+1*B28</f>
+        <v/>
+      </c>
+      <c r="C29">
+        <f>1*C26+1*C28</f>
+        <v/>
       </c>
     </row>
     <row r="30">
@@ -700,11 +708,11 @@
         </is>
       </c>
       <c r="B34">
-        <f>1*B26+1*B31+1*B28+1*B32+1*B33</f>
+        <f>1*B31+1*B32+1*B33</f>
         <v/>
       </c>
       <c r="C34">
-        <f>1*C26+1*C31+1*C28+1*C32+1*C33</f>
+        <f>1*C31+1*C32+1*C33</f>
         <v/>
       </c>
     </row>
@@ -1497,11 +1505,11 @@
         </is>
       </c>
       <c r="B98">
-        <f>1*B96+1*B96+1*B97+1*B97</f>
+        <f>1*B96+1*B97</f>
         <v/>
       </c>
       <c r="C98">
-        <f>1*C96+1*C96+1*C97+1*C97</f>
+        <f>1*C96+1*C97</f>
         <v/>
       </c>
     </row>
@@ -1561,11 +1569,11 @@
         </is>
       </c>
       <c r="B106">
-        <f>1*B103+1*B103+1*B104+1*B104+1*B105+1*B105</f>
+        <f>1*B103+1*B104+1*B105</f>
         <v/>
       </c>
       <c r="C106">
-        <f>1*C103+1*C103+1*C104+1*C104+1*C105+1*C105</f>
+        <f>1*C103+1*C104+1*C105</f>
         <v/>
       </c>
     </row>
@@ -1716,11 +1724,11 @@
         </is>
       </c>
       <c r="B127">
-        <f>1*B116+1*B116+1*B117+1*B117+1*B118+1*B118+1*B119+1*B119+1*B120+1*B120+1*B121+1*B121+1*B123+1*B123+1*B122+1*B122+1*B124+1*B124+1*B125+1*B125+1*B126+1*B126</f>
+        <f>1*B116+1*B117+1*B118+1*B119+1*B120+1*B121+1*B123+1*B122+1*B124+1*B125+1*B126</f>
         <v/>
       </c>
       <c r="C127">
-        <f>1*C116+1*C116+1*C117+1*C117+1*C118+1*C118+1*C119+1*C119+1*C120+1*C120+1*C121+1*C121+1*C123+1*C123+1*C122+1*C122+1*C124+1*C124+1*C125+1*C125+1*C126+1*C126</f>
+        <f>1*C116+1*C117+1*C118+1*C119+1*C120+1*C121+1*C123+1*C122+1*C124+1*C125+1*C126</f>
         <v/>
       </c>
     </row>
@@ -1801,11 +1809,11 @@
         </is>
       </c>
       <c r="B138">
-        <f>1*B129+1*B129+1*B130+1*B130+1*B131+1*B131+1*B132+1*B132+1*B133+1*B133+1*B134+1*B134+1*B136+1*B136+1*B135+1*B135+1*B137+1*B137</f>
+        <f>1*B129+1*B130+1*B131+1*B132+1*B133+1*B134+1*B136+1*B135+1*B137</f>
         <v/>
       </c>
       <c r="C138">
-        <f>1*C129+1*C129+1*C130+1*C130+1*C131+1*C131+1*C132+1*C132+1*C133+1*C133+1*C134+1*C134+1*C136+1*C136+1*C135+1*C135+1*C137+1*C137</f>
+        <f>1*C129+1*C130+1*C131+1*C132+1*C133+1*C134+1*C136+1*C135+1*C137</f>
         <v/>
       </c>
     </row>
